--- a/SIC_model_data.xlsx
+++ b/SIC_model_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cyf25\Downloads\Bayes-paleo-weighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D350504E-6C42-4592-8358-7D520551D340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0161056F-3F69-435C-9D8D-D185ABEEF3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1395,13 +1395,14 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="15.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2058,13 +2059,14 @@
   <dimension ref="A1:G121"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="92.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
